--- a/projects/nahirna-16/out/estimate.xlsx
+++ b/projects/nahirna-16/out/estimate.xlsx
@@ -165,7 +165,17 @@
     <author>Shtroba</author>
   </authors>
   <commentList>
-    <comment ref="E21" authorId="0" shapeId="0">
+    <comment ref="E17" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E18" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0" shapeId="0">
       <text>
         <t>немає ціни</t>
       </text>
@@ -210,7 +220,57 @@
         <t>немає ціни</t>
       </text>
     </comment>
-    <comment ref="E40" authorId="0" shapeId="0">
+    <comment ref="E30" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E31" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E32" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E33" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E34" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E35" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E37" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="E38" authorId="0" shapeId="0">
+      <text>
+        <t>немає ціни</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Встановлення розеток, вимикачів, інтернет- і ТВ-виводів. Ціна уточнюється</t>
+      </text>
+    </comment>
+    <comment ref="E49" authorId="0" shapeId="0">
       <text>
         <t>немає ціни</t>
       </text>
@@ -508,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -938,7 +998,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Автомат 1P (на групу)</t>
+          <t>Вступний автомат, C63 2P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -947,18 +1007,16 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>140</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="n"/>
       <c r="F17" s="6">
         <f>IF(E17="","",D17*E17)</f>
         <v/>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>breaker</t>
+          <t>input.C63 2P</t>
         </is>
       </c>
     </row>
@@ -968,7 +1026,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Вступний автомат 2P 40 A</t>
+          <t>Реле напруги, 63 А</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,16 +1037,14 @@
       <c r="D18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>500</v>
-      </c>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="6">
         <f>IF(E18="","",D18*E18)</f>
         <v/>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>board_kit</t>
+          <t>relay.63 А</t>
         </is>
       </c>
     </row>
@@ -998,7 +1054,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Реле напруги</t>
+          <t>Автомат 1P C10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1007,10 +1063,10 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1500</v>
+        <v>140</v>
       </c>
       <c r="F19" s="6">
         <f>IF(E19="","",D19*E19)</f>
@@ -1018,7 +1074,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>board_kit</t>
+          <t>breaker.C10</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1084,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ПЗВ 2P 40 A 30 мА</t>
+          <t>Дифавтомат 1P+N C10 30 мА</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1039,16 +1095,14 @@
       <c r="D20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="5" t="n">
-        <v>1200</v>
-      </c>
+      <c r="E20" s="5" t="n"/>
       <c r="F20" s="6">
         <f>IF(E20="","",D20*E20)</f>
         <v/>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>board_kit</t>
+          <t>diff.C10 30 мА</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1112,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Розетка із заземленням</t>
+          <t>Автомат 1P C16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1067,16 +1121,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="E21" s="5" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>140</v>
+      </c>
       <c r="F21" s="6">
         <f>IF(E21="","",D21*E21)</f>
         <v/>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>socket</t>
+          <t>breaker.C16</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1142,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Вимикач одноклавішний</t>
+          <t>Дифавтомат 1P+N C16 30 мА</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1095,7 +1151,7 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="6">
@@ -1104,7 +1160,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>switch1</t>
+          <t>diff.C16 30 мА</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1170,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Вимикач двоклавішний</t>
+          <t>Розетка із заземленням</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1123,7 +1179,7 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="6">
@@ -1132,7 +1188,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>switch2</t>
+          <t>socket</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1198,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Вимикач прохідний</t>
+          <t>Вимикач одноклавішний</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1151,7 +1207,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="6">
@@ -1160,7 +1216,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>pass_switch</t>
+          <t>switch1</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1226,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Розетка інтернет</t>
+          <t>Вимикач двоклавішний</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1179,7 +1235,7 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="6">
@@ -1188,7 +1244,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>switch2</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1254,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Рамка 1-постова</t>
+          <t>Вимикач прохідний</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1207,7 +1263,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="6">
@@ -1216,7 +1272,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>frame.1</t>
+          <t>pass_switch</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1282,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Рамка 2-постова</t>
+          <t>Розетка інтернет</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1235,7 +1291,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="6">
@@ -1244,7 +1300,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>frame.2</t>
+          <t>data</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1310,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Рамка 3-постова</t>
+          <t>Рамка 1-постова</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1263,7 +1319,7 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="6">
@@ -1272,7 +1328,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>frame.3</t>
+          <t>frame.1</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1338,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Рамка 4-постова</t>
+          <t>Рамка 2-постова</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1291,7 +1347,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="6">
@@ -1300,130 +1356,157 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
+          <t>frame.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Рамка 3-постова</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6">
+        <f>IF(E30="","",D30*E30)</f>
+        <v/>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>frame.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Рамка 4-постова</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6">
+        <f>IF(E31="","",D31*E31)</f>
+        <v/>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
           <t>frame.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Разом: Матеріали</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" s="8">
-        <f>SUM(F5:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Роботи</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Прокладання кабелю</t>
+          <t>Світильник стельовий</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>669.7</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>30</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E32" s="5" t="n"/>
       <c r="F32" s="6">
         <f>IF(E32="","",D32*E32)</f>
         <v/>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>work.cable</t>
+          <t>light</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Штроба вузька, 1–2 кабелі</t>
+          <t>Світильник точковий</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>200</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E33" s="5" t="n"/>
       <c r="F33" s="6">
         <f>IF(E33="","",D33*E33)</f>
         <v/>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>work.chase</t>
+          <t>downlight</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Світильник підвісний</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Штроба широка, 3–4 кабелі</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>300</v>
-      </c>
+      <c r="E34" s="5" t="n"/>
       <c r="F34" s="6">
         <f>IF(E34="","",D34*E34)</f>
         <v/>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>work.chase_wide</t>
+          <t>pendant</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Свердління проходу крізь стіну</t>
+          <t>Бра</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1434,26 +1517,24 @@
       <c r="D35" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="5" t="n">
-        <v>150</v>
-      </c>
+      <c r="E35" s="5" t="n"/>
       <c r="F35" s="6">
         <f>IF(E35="","",D35*E35)</f>
         <v/>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>work.wall_hole</t>
+          <t>sconce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Свердління і встановлення підрозетника</t>
+          <t>Вивід для підсвітки</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1462,158 +1543,117 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>100</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E36" s="5" t="n"/>
       <c r="F36" s="6">
         <f>IF(E36="","",D36*E36)</f>
         <v/>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>work.socket_box</t>
+          <t>led_output</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Вивід кабелю до техніки</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Монтаж коробки з опресуванням</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>450</v>
-      </c>
+      <c r="E37" s="5" t="n"/>
       <c r="F37" s="6">
         <f>IF(E37="","",D37*E37)</f>
         <v/>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>work.junction_box</t>
+          <t>outlet</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Встановлення щита</t>
+          <t>LED-підсвітка</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>2500</v>
-      </c>
+        <v>6.35</v>
+      </c>
+      <c r="E38" s="5" t="n"/>
       <c r="F38" s="6">
         <f>IF(E38="","",D38*E38)</f>
         <v/>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>work.board_install</t>
+          <t>led_strip</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>8</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Збирання щита</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>мод.</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="F39" s="6">
-        <f>IF(E39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>work.board_module</t>
-        </is>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Разом: Матеріали</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" s="8">
+        <f>SUM(F5:F38)</f>
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>9</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Встановлення механізмів</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(E40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>work.mechanism</t>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Роботи</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Маркування кінців кабелю</t>
+          <t>Прокладання кабелю</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>268</v>
+        <v>669.7</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F41" s="6">
         <f>IF(E41="","",D41*E41)</f>
@@ -1621,29 +1661,29 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>work.marking</t>
+          <t>work.cable</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Вимірювання опору ізоляції з протоколом</t>
+          <t>Штроба вузька, 1–2 кабелі</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>гр.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>18</v>
+        <v>85.8</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F42" s="6">
         <f>IF(E42="","",D42*E42)</f>
@@ -1651,117 +1691,313 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
+          <t>work.chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Штроба широка, 3–4 кабелі</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="F43" s="6">
+        <f>IF(E43="","",D43*E43)</f>
+        <v/>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>work.chase_wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Свердління проходу крізь стіну</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="F44" s="6">
+        <f>IF(E44="","",D44*E44)</f>
+        <v/>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>work.wall_hole</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Свердління і встановлення підрозетника</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" s="6">
+        <f>IF(E45="","",D45*E45)</f>
+        <v/>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>work.socket_box</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Монтаж коробки з опресуванням</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F46" s="6">
+        <f>IF(E46="","",D46*E46)</f>
+        <v/>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>work.junction_box</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Встановлення щита</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F47" s="6">
+        <f>IF(E47="","",D47*E47)</f>
+        <v/>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>work.board_install</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Збирання щита</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>мод.</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="F48" s="6">
+        <f>IF(E48="","",D48*E48)</f>
+        <v/>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>work.board_module</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>9</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Встановлення механізмів</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="6">
+        <f>IF(E49="","",D49*E49)</f>
+        <v/>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>work.mechanism</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Маркування кінців кабелю</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>268</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="6">
+        <f>IF(E50="","",D50*E50)</f>
+        <v/>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>work.marking</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Вимірювання опору ізоляції з протоколом</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>гр.</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="F51" s="6">
+        <f>IF(E51="","",D51*E51)</f>
+        <v/>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
           <t>work.insulation_test</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Разом: Роботи</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" s="8">
-        <f>SUM(F32:F42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Усього, грн</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" s="10">
-        <f>F30+F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Без ціни: 10 поз. — до підсумку не входять, потрібна ціна в prices.yaml.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Ціни: prices.yaml (2026-10) — орієнтир за ринком Києва, звірити з постачальником і бригадою</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Кабель — із запасом 15 %; прокладання — за фактичною довжиною</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Штроби: спільна, якщо спуски ближче 150 мм, до 4 кабелів; до 2 кабелів — вузька, більше — широка; силові і слабкострумові — в різних штробах</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Проходи крізь стіни — над дверима і прорізами для трас по стелі, до 4 кабелів в отворі; траси по підлозі йдуть під прорізом без свердління</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Кріплення кабелю — крок 400 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Опресування: у кожній коробці L, N, PE і по з'єднанню на клавішу вимикача</t>
-        </is>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Разом: Роботи</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" s="8">
+        <f>SUM(F41:F51)</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Виведення кабелю в щиті — до підлоги (1700 мм), на інших підключеннях — 200 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Окремі лінії від щита без коробок: QF15, QF16, QF17, QF18</t>
-        </is>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Усього, грн</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" s="10">
+        <f>F39+F52</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Коробки у вологих приміщеннях — IP44: 4 шт</t>
+          <t>Без ціни: 21 поз. — до підсумку не входять, потрібна ціна в prices.yaml.</t>
         </is>
       </c>
     </row>
@@ -1769,13 +2005,101 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Не входить: LED-підсвітка (стрічка, профіль, блоки живлення), світильники, введення живлення</t>
+          <t>Ціни: prices.yaml (2026-10) — орієнтир за ринком Києва, звірити з постачальником і бригадою</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
+        <is>
+          <t>Кабель — із запасом 15 %; прокладання — за фактичною довжиною</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Штроби: спільна, якщо спуски ближче 150 мм, до 4 кабелів; до 2 кабелів — вузька, більше — широка; силові і слабкострумові — в різних штробах</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Проходи крізь стіни — над дверима і прорізами для трас по стелі, до 4 кабелів в отворі; траси по підлозі йдуть під прорізом без свердління</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Кріплення кабелю — крок 400 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Опресування: у кожній коробці L, N, PE і по з'єднанню на клавішу вимикача</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Щит — за складом аркуша «Щит»: апарати за видами і номіналами</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Виведення кабелю в щиті — до підлоги (1700 мм), на інших підключеннях — 200 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>board_kit у prices.yaml не використовується: склад щита — з аркуша «Щит», ціни апаратів — ключами input, relay, spd, rcd, changeover, ats, feed, breaker, diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Окремі лінії від щита без коробок: QF15, QF16, QF17, QF18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Коробки у вологих приміщеннях — IP44: 4 шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Не входить: профіль і блоки живлення LED, монтаж світильників, введення живлення</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
         <is>
           <t>Відкриті питання з електрики: q6 — обсяги можуть змінитися</t>
         </is>
